--- a/Requirments/SRS.xlsx
+++ b/Requirments/SRS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\ITI\Online-Mobile-Store-WebSite\Requirments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SW Testing-iti 9m\Online-Mobile-Store-WebSite\Requirments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9EE843-2ADC-4B44-962E-0B074A67276F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{648EC5FF-8C10-48BA-8C3A-1411BD0D8E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,9 +121,6 @@
     <t>SRS_Reg_018</t>
   </si>
   <si>
-    <t>The username shall contain only alphabetic characters (a-z, A-Z).</t>
-  </si>
-  <si>
     <t>The username shall not contain spaces.</t>
   </si>
   <si>
@@ -468,6 +465,9 @@
   </si>
   <si>
     <t>The user shall be able to enter a username, email address, password, confirm password, address, phone number, National ID and User Type.</t>
+  </si>
+  <si>
+    <t>The username shall contain only alphabetic characters (a-z, A-Z)..</t>
   </si>
 </sst>
 </file>
@@ -859,7 +859,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>3</v>
@@ -870,7 +870,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>33</v>
+        <v>148</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>4</v>
@@ -881,7 +881,7 @@
         <v>17</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>4</v>
@@ -892,7 +892,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>5</v>
@@ -903,7 +903,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>3</v>
@@ -914,7 +914,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>12</v>
@@ -925,7 +925,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>6</v>
@@ -936,7 +936,7 @@
         <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>7</v>
@@ -947,7 +947,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>8</v>
@@ -958,7 +958,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>8</v>
@@ -969,7 +969,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
@@ -980,7 +980,7 @@
         <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
@@ -991,7 +991,7 @@
         <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>10</v>
@@ -1002,7 +1002,7 @@
         <v>28</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>11</v>
@@ -1013,7 +1013,7 @@
         <v>29</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>11</v>
@@ -1024,7 +1024,7 @@
         <v>30</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>13</v>
@@ -1035,7 +1035,7 @@
         <v>31</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>14</v>
@@ -1046,7 +1046,7 @@
         <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>14</v>
@@ -1054,431 +1054,431 @@
     </row>
     <row r="20" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="C25" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
